--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО КАМЕНАР/КМЕТСТВО КАМЕНАР.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В3914РТ</t>
@@ -79,28 +73,13 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:38:00</t>
-  </si>
-  <si>
-    <t>11:40:00</t>
-  </si>
-  <si>
-    <t>10:44:00</t>
-  </si>
-  <si>
-    <t>3236592676 3236592676</t>
-  </si>
-  <si>
-    <t>3236592677 3236592677</t>
-  </si>
-  <si>
-    <t>3236956215 3236956215</t>
-  </si>
-  <si>
-    <t>3237049758 3237049758</t>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>14:52</t>
+  </si>
+  <si>
+    <t>14:53</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО КАМЕНАР</t>
@@ -523,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -532,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,257 +560,201 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>31.06</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="H2" s="1">
+        <v>49.075</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="J2" s="1">
+        <v>50.007</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2">
+        <v>182966</v>
+      </c>
+      <c r="M2">
+        <v>169745</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3">
+        <v>30.86</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H3" s="1">
+        <v>49.067</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J3" s="1">
+        <v>49.993</v>
+      </c>
+      <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>33.33</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="L3">
+        <v>183228</v>
+      </c>
+      <c r="M3">
+        <v>172800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H4" s="1">
+        <v>15.709</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J4" s="1">
+        <v>16.006</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="I2" s="1">
-        <v>50.995</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
-        <v>51.995</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>172801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>182589</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46253</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>11.76</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>17.993</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>18.346</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>71.8</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.58567</v>
+      </c>
+      <c r="E9" s="7">
+        <v>113.85</v>
+      </c>
+      <c r="F9" s="7">
+        <v>116.01</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46260</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>10.76</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="I4" s="1">
-        <v>16.678</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="K4" s="1">
-        <v>17.001</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46262</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5">
-        <v>10.69</v>
-      </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16.676</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="K5" s="1">
-        <v>16.997</v>
-      </c>
-      <c r="L5" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="7">
-        <v>66.54000000000001</v>
-      </c>
-      <c r="C10" s="8">
-        <v>4</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1.53805</v>
-      </c>
-      <c r="E10" s="7">
-        <v>102.34</v>
-      </c>
-      <c r="F10" s="7">
-        <v>104.34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="11">
-        <v>66.54000000000001</v>
-      </c>
-      <c r="C11" s="12">
-        <v>4</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="11">
-        <v>102.34</v>
-      </c>
-      <c r="F11" s="11">
-        <v>104.34</v>
+      <c r="B10" s="11">
+        <v>71.8</v>
+      </c>
+      <c r="C10" s="12">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
+        <v>113.85</v>
+      </c>
+      <c r="F10" s="11">
+        <v>116.01</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
